--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
@@ -420,16 +420,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.2478632478632479</v>
+        <v>0.2564102564102564</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.2887323943661972</v>
+        <v>0.2957746478873239</v>
       </c>
       <c r="D2">
-        <v>0.7769230769230769</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="E2">
         <v>117</v>
